--- a/bajada_tipo_neg.xlsx
+++ b/bajada_tipo_neg.xlsx
@@ -424,13 +424,13 @@
         <v>4</v>
       </c>
       <c r="D1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="n">
+      <c r="F1" t="n">
         <v>1</v>
-      </c>
-      <c r="F1" t="n">
-        <v>5</v>
       </c>
       <c r="G1" t="n">
         <v>2</v>
@@ -454,17 +454,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>SL - SUPERMERCADO LOCAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>MK - MINIMARKET</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>CA - CARNICERÍA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SL - SUPERMERCADO LOCAL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37849676132</v>
+        <v>42273753537</v>
       </c>
       <c r="C3" t="n">
-        <v>4629761806</v>
+        <v>7725994817</v>
       </c>
       <c r="D3" t="n">
-        <v>2822856011</v>
+        <v>5860867220</v>
       </c>
       <c r="E3" t="n">
-        <v>1202038875</v>
+        <v>5635897477</v>
       </c>
       <c r="F3" t="n">
-        <v>724713150</v>
+        <v>1756100571</v>
       </c>
       <c r="G3" t="n">
-        <v>318430434</v>
+        <v>658472867</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7314308402.653605</v>
+        <v>8145483234.116655</v>
       </c>
       <c r="C4" t="n">
-        <v>990626993.496168</v>
+        <v>1650661956.853402</v>
       </c>
       <c r="D4" t="n">
-        <v>548172052.5515879</v>
+        <v>1109943712.436262</v>
       </c>
       <c r="E4" t="n">
-        <v>226608291.7471467</v>
+        <v>1091793390.667093</v>
       </c>
       <c r="F4" t="n">
-        <v>149110352.5671607</v>
+        <v>331390162.4521999</v>
       </c>
       <c r="G4" t="n">
-        <v>59658026.49603502</v>
+        <v>138179415.2322579</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1932462612664134</v>
+        <v>0.192684172863603</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2139693217504953</v>
+        <v>0.2136504095526112</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1941905823093674</v>
+        <v>0.1893821632144504</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1885199359689151</v>
+        <v>0.1937213008438643</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2057508582080519</v>
+        <v>0.1887079634986349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1873502659486217</v>
+        <v>0.2098483053095305</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30570</v>
+        <v>31173</v>
       </c>
       <c r="C6" t="n">
-        <v>2159</v>
+        <v>2485</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>207</v>
       </c>
       <c r="E6" t="n">
-        <v>841</v>
+        <v>1223</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>901</v>
       </c>
       <c r="G6" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1238131.374942754</v>
+        <v>1356101.547396786</v>
       </c>
       <c r="C7" t="n">
-        <v>2144401.021769338</v>
+        <v>3109052.240241449</v>
       </c>
       <c r="D7" t="n">
-        <v>2928273.87033195</v>
+        <v>28313368.21256039</v>
       </c>
       <c r="E7" t="n">
-        <v>1429297.116527943</v>
+        <v>4608256.318070319</v>
       </c>
       <c r="F7" t="n">
-        <v>19071398.68421053</v>
+        <v>1949057.237513873</v>
       </c>
       <c r="G7" t="n">
-        <v>2274503.1</v>
+        <v>3990744.648484848</v>
       </c>
     </row>
   </sheetData>
